--- a/AAII_Financials/Yearly/SSAAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSAAY_YR_FIN.xlsx
@@ -932,7 +932,7 @@
         <v>344400</v>
       </c>
       <c r="E15" s="3">
-        <v>301700</v>
+        <v>301600</v>
       </c>
       <c r="F15" s="3">
         <v>293100</v>
@@ -1091,7 +1091,7 @@
         <v>991400</v>
       </c>
       <c r="E21" s="3">
-        <v>986500</v>
+        <v>986400</v>
       </c>
       <c r="F21" s="3">
         <v>1883200</v>
@@ -2907,7 +2907,7 @@
         <v>425800</v>
       </c>
       <c r="E83" s="3">
-        <v>366600</v>
+        <v>366500</v>
       </c>
       <c r="F83" s="3">
         <v>352700</v>
